--- a/Data/mappings/ei312/ei_iw_mapping.xlsx
+++ b/Data/mappings/ei312/ei_iw_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11max\PycharmProjects\IW_Reborn\Data\mappings\ei312\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD93561-E623-47B5-BF90-3337061F811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8498C1-8F40-4692-AFCB-B8FE88CFFE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5405" uniqueCount="2646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5739" uniqueCount="2652">
   <si>
     <t>ecoinvent name</t>
   </si>
@@ -7974,6 +7974,24 @@
   </si>
   <si>
     <t>Lithium (I)</t>
+  </si>
+  <si>
+    <t>Bauxite</t>
+  </si>
+  <si>
+    <t>Gas, natural/m3</t>
+  </si>
+  <si>
+    <t>Metamorphous rock, graphite containing</t>
+  </si>
+  <si>
+    <t>Wood, unspecified, standing/m3</t>
+  </si>
+  <si>
+    <t>Baddeleyite</t>
+  </si>
+  <si>
+    <t>Sand</t>
   </si>
 </sst>
 </file>
@@ -8990,6 +9008,9 @@
       <c r="A59" t="s">
         <v>61</v>
       </c>
+      <c r="B59" t="s">
+        <v>2646</v>
+      </c>
       <c r="C59" t="s">
         <v>2641</v>
       </c>
@@ -8998,6 +9019,9 @@
       <c r="A60" t="s">
         <v>62</v>
       </c>
+      <c r="B60" t="s">
+        <v>59</v>
+      </c>
       <c r="C60" t="s">
         <v>2641</v>
       </c>
@@ -9105,6 +9129,9 @@
       <c r="A70" t="s">
         <v>72</v>
       </c>
+      <c r="B70" t="s">
+        <v>1456</v>
+      </c>
       <c r="C70" t="s">
         <v>2641</v>
       </c>
@@ -9354,6 +9381,9 @@
       <c r="A94" t="s">
         <v>96</v>
       </c>
+      <c r="B94" t="s">
+        <v>2317</v>
+      </c>
       <c r="C94" t="s">
         <v>2641</v>
       </c>
@@ -9392,6 +9422,9 @@
       <c r="A98" t="s">
         <v>100</v>
       </c>
+      <c r="B98" t="s">
+        <v>1463</v>
+      </c>
       <c r="C98" t="s">
         <v>2641</v>
       </c>
@@ -9814,6 +9847,9 @@
       <c r="A138" t="s">
         <v>140</v>
       </c>
+      <c r="B138" t="s">
+        <v>140</v>
+      </c>
       <c r="C138" t="s">
         <v>2641</v>
       </c>
@@ -10099,6 +10135,9 @@
       <c r="A165" t="s">
         <v>167</v>
       </c>
+      <c r="B165" t="s">
+        <v>166</v>
+      </c>
       <c r="C165" t="s">
         <v>2641</v>
       </c>
@@ -10126,6 +10165,9 @@
       <c r="A168" t="s">
         <v>170</v>
       </c>
+      <c r="B168" t="s">
+        <v>1476</v>
+      </c>
       <c r="C168" t="s">
         <v>2641</v>
       </c>
@@ -10462,6 +10504,9 @@
       <c r="A201" t="s">
         <v>203</v>
       </c>
+      <c r="B201" t="s">
+        <v>203</v>
+      </c>
       <c r="C201" t="s">
         <v>2641</v>
       </c>
@@ -10829,6 +10874,9 @@
       <c r="A236" t="s">
         <v>238</v>
       </c>
+      <c r="B236" t="s">
+        <v>235</v>
+      </c>
       <c r="C236" t="s">
         <v>2641</v>
       </c>
@@ -10837,6 +10885,9 @@
       <c r="A237" t="s">
         <v>239</v>
       </c>
+      <c r="B237" t="s">
+        <v>235</v>
+      </c>
       <c r="C237" t="s">
         <v>2641</v>
       </c>
@@ -10875,6 +10926,9 @@
       <c r="A241" t="s">
         <v>243</v>
       </c>
+      <c r="B241" t="s">
+        <v>1483</v>
+      </c>
       <c r="C241" t="s">
         <v>2641</v>
       </c>
@@ -10891,6 +10945,9 @@
       <c r="A243" t="s">
         <v>245</v>
       </c>
+      <c r="B243" t="s">
+        <v>1484</v>
+      </c>
       <c r="C243" t="s">
         <v>2641</v>
       </c>
@@ -10899,6 +10956,9 @@
       <c r="A244" t="s">
         <v>246</v>
       </c>
+      <c r="B244" t="s">
+        <v>1485</v>
+      </c>
       <c r="C244" t="s">
         <v>2641</v>
       </c>
@@ -10907,6 +10967,9 @@
       <c r="A245" t="s">
         <v>247</v>
       </c>
+      <c r="B245" t="s">
+        <v>1486</v>
+      </c>
       <c r="C245" t="s">
         <v>2641</v>
       </c>
@@ -11003,6 +11066,9 @@
       <c r="A254" t="s">
         <v>256</v>
       </c>
+      <c r="B254" t="s">
+        <v>1487</v>
+      </c>
       <c r="C254" t="s">
         <v>2641</v>
       </c>
@@ -11011,6 +11077,9 @@
       <c r="A255" t="s">
         <v>257</v>
       </c>
+      <c r="B255" t="s">
+        <v>1748</v>
+      </c>
       <c r="C255" t="s">
         <v>2641</v>
       </c>
@@ -11030,6 +11099,9 @@
       <c r="A257" t="s">
         <v>259</v>
       </c>
+      <c r="B257" t="s">
+        <v>258</v>
+      </c>
       <c r="C257" t="s">
         <v>2641</v>
       </c>
@@ -11038,6 +11110,9 @@
       <c r="A258" t="s">
         <v>260</v>
       </c>
+      <c r="B258" t="s">
+        <v>258</v>
+      </c>
       <c r="C258" t="s">
         <v>2641</v>
       </c>
@@ -11090,6 +11165,9 @@
       <c r="A263" t="s">
         <v>265</v>
       </c>
+      <c r="B263" t="s">
+        <v>1491</v>
+      </c>
       <c r="C263" t="s">
         <v>2641</v>
       </c>
@@ -11109,6 +11187,9 @@
       <c r="A265" t="s">
         <v>267</v>
       </c>
+      <c r="B265" t="s">
+        <v>266</v>
+      </c>
       <c r="C265" t="s">
         <v>2641</v>
       </c>
@@ -11117,6 +11198,9 @@
       <c r="A266" t="s">
         <v>268</v>
       </c>
+      <c r="B266" t="s">
+        <v>266</v>
+      </c>
       <c r="C266" t="s">
         <v>2641</v>
       </c>
@@ -11125,6 +11209,9 @@
       <c r="A267" t="s">
         <v>269</v>
       </c>
+      <c r="B267" t="s">
+        <v>266</v>
+      </c>
       <c r="C267" t="s">
         <v>2641</v>
       </c>
@@ -11133,6 +11220,9 @@
       <c r="A268" t="s">
         <v>270</v>
       </c>
+      <c r="B268" t="s">
+        <v>266</v>
+      </c>
       <c r="C268" t="s">
         <v>2641</v>
       </c>
@@ -11141,6 +11231,9 @@
       <c r="A269" t="s">
         <v>271</v>
       </c>
+      <c r="B269" t="s">
+        <v>266</v>
+      </c>
       <c r="C269" t="s">
         <v>2641</v>
       </c>
@@ -11149,6 +11242,9 @@
       <c r="A270" t="s">
         <v>272</v>
       </c>
+      <c r="B270" t="s">
+        <v>266</v>
+      </c>
       <c r="C270" t="s">
         <v>2641</v>
       </c>
@@ -11157,6 +11253,9 @@
       <c r="A271" t="s">
         <v>273</v>
       </c>
+      <c r="B271" t="s">
+        <v>266</v>
+      </c>
       <c r="C271" t="s">
         <v>2641</v>
       </c>
@@ -11165,6 +11264,9 @@
       <c r="A272" t="s">
         <v>274</v>
       </c>
+      <c r="B272" t="s">
+        <v>266</v>
+      </c>
       <c r="C272" t="s">
         <v>2641</v>
       </c>
@@ -11173,6 +11275,9 @@
       <c r="A273" t="s">
         <v>275</v>
       </c>
+      <c r="B273" t="s">
+        <v>266</v>
+      </c>
       <c r="C273" t="s">
         <v>2641</v>
       </c>
@@ -11181,6 +11286,9 @@
       <c r="A274" t="s">
         <v>276</v>
       </c>
+      <c r="B274" t="s">
+        <v>266</v>
+      </c>
       <c r="C274" t="s">
         <v>2641</v>
       </c>
@@ -11189,6 +11297,9 @@
       <c r="A275" t="s">
         <v>277</v>
       </c>
+      <c r="B275" t="s">
+        <v>266</v>
+      </c>
       <c r="C275" t="s">
         <v>2641</v>
       </c>
@@ -11197,6 +11308,9 @@
       <c r="A276" t="s">
         <v>278</v>
       </c>
+      <c r="B276" t="s">
+        <v>266</v>
+      </c>
       <c r="C276" t="s">
         <v>2641</v>
       </c>
@@ -11205,6 +11319,9 @@
       <c r="A277" t="s">
         <v>279</v>
       </c>
+      <c r="B277" t="s">
+        <v>266</v>
+      </c>
       <c r="C277" t="s">
         <v>2641</v>
       </c>
@@ -11224,6 +11341,9 @@
       <c r="A279" t="s">
         <v>281</v>
       </c>
+      <c r="B279" t="s">
+        <v>266</v>
+      </c>
       <c r="C279" t="s">
         <v>2641</v>
       </c>
@@ -11232,6 +11352,9 @@
       <c r="A280" t="s">
         <v>282</v>
       </c>
+      <c r="B280" t="s">
+        <v>266</v>
+      </c>
       <c r="C280" t="s">
         <v>2641</v>
       </c>
@@ -11588,6 +11711,9 @@
       <c r="A314" t="s">
         <v>316</v>
       </c>
+      <c r="B314" t="s">
+        <v>1511</v>
+      </c>
       <c r="C314" t="s">
         <v>2641</v>
       </c>
@@ -12276,6 +12402,9 @@
       <c r="A379" t="s">
         <v>381</v>
       </c>
+      <c r="B379" t="s">
+        <v>1513</v>
+      </c>
       <c r="C379" t="s">
         <v>2641</v>
       </c>
@@ -12832,6 +12961,9 @@
       <c r="A432" t="s">
         <v>434</v>
       </c>
+      <c r="B432" t="s">
+        <v>1518</v>
+      </c>
       <c r="C432" t="s">
         <v>2641</v>
       </c>
@@ -12859,6 +12991,9 @@
       <c r="A435" t="s">
         <v>437</v>
       </c>
+      <c r="B435" t="s">
+        <v>1520</v>
+      </c>
       <c r="C435" t="s">
         <v>2641</v>
       </c>
@@ -13307,6 +13442,9 @@
       <c r="A476" t="s">
         <v>478</v>
       </c>
+      <c r="B476" t="s">
+        <v>477</v>
+      </c>
       <c r="C476" t="s">
         <v>2641</v>
       </c>
@@ -13315,6 +13453,9 @@
       <c r="A477" t="s">
         <v>479</v>
       </c>
+      <c r="B477" t="s">
+        <v>477</v>
+      </c>
       <c r="C477" t="s">
         <v>2641</v>
       </c>
@@ -13353,6 +13494,9 @@
       <c r="A481" t="s">
         <v>483</v>
       </c>
+      <c r="B481" t="s">
+        <v>1526</v>
+      </c>
       <c r="C481" t="s">
         <v>2641</v>
       </c>
@@ -13626,6 +13770,9 @@
       <c r="A508" t="s">
         <v>510</v>
       </c>
+      <c r="B508" t="s">
+        <v>1531</v>
+      </c>
       <c r="C508" t="s">
         <v>2641</v>
       </c>
@@ -13634,6 +13781,9 @@
       <c r="A509" t="s">
         <v>511</v>
       </c>
+      <c r="B509" t="s">
+        <v>1533</v>
+      </c>
       <c r="C509" t="s">
         <v>2641</v>
       </c>
@@ -13642,6 +13792,9 @@
       <c r="A510" t="s">
         <v>512</v>
       </c>
+      <c r="B510" t="s">
+        <v>1533</v>
+      </c>
       <c r="C510" t="s">
         <v>2641</v>
       </c>
@@ -13650,6 +13803,9 @@
       <c r="A511" t="s">
         <v>513</v>
       </c>
+      <c r="B511" t="s">
+        <v>2646</v>
+      </c>
       <c r="C511" t="s">
         <v>2641</v>
       </c>
@@ -13658,6 +13814,9 @@
       <c r="A512" t="s">
         <v>514</v>
       </c>
+      <c r="B512" t="s">
+        <v>2646</v>
+      </c>
       <c r="C512" t="s">
         <v>2641</v>
       </c>
@@ -13666,6 +13825,9 @@
       <c r="A513" t="s">
         <v>515</v>
       </c>
+      <c r="B513" t="s">
+        <v>2647</v>
+      </c>
       <c r="C513" t="s">
         <v>2641</v>
       </c>
@@ -13674,6 +13836,9 @@
       <c r="A514" t="s">
         <v>516</v>
       </c>
+      <c r="B514" t="s">
+        <v>2647</v>
+      </c>
       <c r="C514" t="s">
         <v>2641</v>
       </c>
@@ -13745,6 +13910,9 @@
       <c r="A521" t="s">
         <v>523</v>
       </c>
+      <c r="B521" t="s">
+        <v>522</v>
+      </c>
       <c r="C521" t="s">
         <v>2641</v>
       </c>
@@ -13753,6 +13921,9 @@
       <c r="A522" t="s">
         <v>524</v>
       </c>
+      <c r="B522" t="s">
+        <v>522</v>
+      </c>
       <c r="C522" t="s">
         <v>2641</v>
       </c>
@@ -13761,6 +13932,9 @@
       <c r="A523" t="s">
         <v>525</v>
       </c>
+      <c r="B523" t="s">
+        <v>522</v>
+      </c>
       <c r="C523" t="s">
         <v>2641</v>
       </c>
@@ -13769,6 +13943,9 @@
       <c r="A524" t="s">
         <v>526</v>
       </c>
+      <c r="B524" t="s">
+        <v>522</v>
+      </c>
       <c r="C524" t="s">
         <v>2641</v>
       </c>
@@ -13777,6 +13954,9 @@
       <c r="A525" t="s">
         <v>527</v>
       </c>
+      <c r="B525" t="s">
+        <v>522</v>
+      </c>
       <c r="C525" t="s">
         <v>2641</v>
       </c>
@@ -13785,6 +13965,9 @@
       <c r="A526" t="s">
         <v>528</v>
       </c>
+      <c r="B526" t="s">
+        <v>522</v>
+      </c>
       <c r="C526" t="s">
         <v>2641</v>
       </c>
@@ -13793,6 +13976,9 @@
       <c r="A527" t="s">
         <v>529</v>
       </c>
+      <c r="B527" t="s">
+        <v>522</v>
+      </c>
       <c r="C527" t="s">
         <v>2641</v>
       </c>
@@ -13801,6 +13987,9 @@
       <c r="A528" t="s">
         <v>530</v>
       </c>
+      <c r="B528" t="s">
+        <v>522</v>
+      </c>
       <c r="C528" t="s">
         <v>2641</v>
       </c>
@@ -13809,6 +13998,9 @@
       <c r="A529" t="s">
         <v>531</v>
       </c>
+      <c r="B529" t="s">
+        <v>522</v>
+      </c>
       <c r="C529" t="s">
         <v>2641</v>
       </c>
@@ -13817,6 +14009,9 @@
       <c r="A530" t="s">
         <v>532</v>
       </c>
+      <c r="B530" t="s">
+        <v>522</v>
+      </c>
       <c r="C530" t="s">
         <v>2641</v>
       </c>
@@ -13825,6 +14020,9 @@
       <c r="A531" t="s">
         <v>533</v>
       </c>
+      <c r="B531" t="s">
+        <v>522</v>
+      </c>
       <c r="C531" t="s">
         <v>2641</v>
       </c>
@@ -13833,6 +14031,9 @@
       <c r="A532" t="s">
         <v>534</v>
       </c>
+      <c r="B532" t="s">
+        <v>522</v>
+      </c>
       <c r="C532" t="s">
         <v>2641</v>
       </c>
@@ -13841,6 +14042,9 @@
       <c r="A533" t="s">
         <v>535</v>
       </c>
+      <c r="B533" t="s">
+        <v>522</v>
+      </c>
       <c r="C533" t="s">
         <v>2641</v>
       </c>
@@ -13849,6 +14053,9 @@
       <c r="A534" t="s">
         <v>536</v>
       </c>
+      <c r="B534" t="s">
+        <v>522</v>
+      </c>
       <c r="C534" t="s">
         <v>2641</v>
       </c>
@@ -13857,6 +14064,9 @@
       <c r="A535" t="s">
         <v>537</v>
       </c>
+      <c r="B535" t="s">
+        <v>522</v>
+      </c>
       <c r="C535" t="s">
         <v>2641</v>
       </c>
@@ -13865,6 +14075,9 @@
       <c r="A536" t="s">
         <v>538</v>
       </c>
+      <c r="B536" t="s">
+        <v>1553</v>
+      </c>
       <c r="C536" t="s">
         <v>2641</v>
       </c>
@@ -13873,6 +14086,9 @@
       <c r="A537" t="s">
         <v>539</v>
       </c>
+      <c r="B537" t="s">
+        <v>1555</v>
+      </c>
       <c r="C537" t="s">
         <v>2641</v>
       </c>
@@ -13892,6 +14108,9 @@
       <c r="A539" t="s">
         <v>541</v>
       </c>
+      <c r="B539" t="s">
+        <v>1556</v>
+      </c>
       <c r="C539" t="s">
         <v>2641</v>
       </c>
@@ -13935,6 +14154,9 @@
       <c r="A544" t="s">
         <v>546</v>
       </c>
+      <c r="B544" t="s">
+        <v>546</v>
+      </c>
       <c r="C544" t="s">
         <v>2641</v>
       </c>
@@ -13943,6 +14165,9 @@
       <c r="A545" t="s">
         <v>547</v>
       </c>
+      <c r="B545" t="s">
+        <v>546</v>
+      </c>
       <c r="C545" t="s">
         <v>2641</v>
       </c>
@@ -14306,6 +14531,9 @@
       <c r="A581" t="s">
         <v>583</v>
       </c>
+      <c r="B581" t="s">
+        <v>1563</v>
+      </c>
       <c r="C581" t="s">
         <v>2641</v>
       </c>
@@ -14472,6 +14700,9 @@
       <c r="A598" t="s">
         <v>600</v>
       </c>
+      <c r="B598" t="s">
+        <v>599</v>
+      </c>
       <c r="C598" t="s">
         <v>2641</v>
       </c>
@@ -14480,6 +14711,9 @@
       <c r="A599" t="s">
         <v>601</v>
       </c>
+      <c r="B599" t="s">
+        <v>599</v>
+      </c>
       <c r="C599" t="s">
         <v>2641</v>
       </c>
@@ -14488,6 +14722,9 @@
       <c r="A600" t="s">
         <v>602</v>
       </c>
+      <c r="B600" t="s">
+        <v>599</v>
+      </c>
       <c r="C600" t="s">
         <v>2641</v>
       </c>
@@ -14597,6 +14834,9 @@
       <c r="A611" t="s">
         <v>613</v>
       </c>
+      <c r="B611" t="s">
+        <v>1570</v>
+      </c>
       <c r="C611" t="s">
         <v>2641</v>
       </c>
@@ -14605,6 +14845,9 @@
       <c r="A612" t="s">
         <v>614</v>
       </c>
+      <c r="B612" t="s">
+        <v>1572</v>
+      </c>
       <c r="C612" t="s">
         <v>2641</v>
       </c>
@@ -14730,6 +14973,9 @@
       <c r="A625" t="s">
         <v>627</v>
       </c>
+      <c r="B625" t="s">
+        <v>626</v>
+      </c>
       <c r="C625" t="s">
         <v>2641</v>
       </c>
@@ -14776,6 +15022,9 @@
       <c r="A630" t="s">
         <v>632</v>
       </c>
+      <c r="B630" t="s">
+        <v>631</v>
+      </c>
       <c r="C630" t="s">
         <v>2641</v>
       </c>
@@ -14784,6 +15033,9 @@
       <c r="A631" t="s">
         <v>633</v>
       </c>
+      <c r="B631" t="s">
+        <v>631</v>
+      </c>
       <c r="C631" t="s">
         <v>2641</v>
       </c>
@@ -14792,6 +15044,9 @@
       <c r="A632" t="s">
         <v>634</v>
       </c>
+      <c r="B632" t="s">
+        <v>631</v>
+      </c>
       <c r="C632" t="s">
         <v>2641</v>
       </c>
@@ -14800,6 +15055,9 @@
       <c r="A633" t="s">
         <v>635</v>
       </c>
+      <c r="B633" t="s">
+        <v>631</v>
+      </c>
       <c r="C633" t="s">
         <v>2641</v>
       </c>
@@ -14874,6 +15132,9 @@
       <c r="A640" t="s">
         <v>642</v>
       </c>
+      <c r="B640" t="s">
+        <v>640</v>
+      </c>
       <c r="C640" t="s">
         <v>2641</v>
       </c>
@@ -14904,6 +15165,9 @@
       <c r="A643" t="s">
         <v>645</v>
       </c>
+      <c r="B643" t="s">
+        <v>2457</v>
+      </c>
       <c r="C643" t="s">
         <v>2641</v>
       </c>
@@ -14931,6 +15195,9 @@
       <c r="A646" t="s">
         <v>648</v>
       </c>
+      <c r="B646" t="s">
+        <v>646</v>
+      </c>
       <c r="C646" t="s">
         <v>2641</v>
       </c>
@@ -14939,6 +15206,9 @@
       <c r="A647" t="s">
         <v>649</v>
       </c>
+      <c r="B647" t="s">
+        <v>646</v>
+      </c>
       <c r="C647" t="s">
         <v>2641</v>
       </c>
@@ -15024,6 +15294,9 @@
       <c r="A655" t="s">
         <v>657</v>
       </c>
+      <c r="B655" t="s">
+        <v>656</v>
+      </c>
       <c r="C655" t="s">
         <v>2641</v>
       </c>
@@ -15232,6 +15505,9 @@
       <c r="A675" t="s">
         <v>677</v>
       </c>
+      <c r="B675" t="s">
+        <v>2648</v>
+      </c>
       <c r="C675" t="s">
         <v>2641</v>
       </c>
@@ -15798,6 +16074,9 @@
       <c r="A727" t="s">
         <v>729</v>
       </c>
+      <c r="B727" t="s">
+        <v>728</v>
+      </c>
       <c r="C727" t="s">
         <v>2641</v>
       </c>
@@ -15806,6 +16085,9 @@
       <c r="A728" t="s">
         <v>730</v>
       </c>
+      <c r="B728" t="s">
+        <v>728</v>
+      </c>
       <c r="C728" t="s">
         <v>2641</v>
       </c>
@@ -15814,6 +16096,9 @@
       <c r="A729" t="s">
         <v>731</v>
       </c>
+      <c r="B729" t="s">
+        <v>728</v>
+      </c>
       <c r="C729" t="s">
         <v>2641</v>
       </c>
@@ -15822,6 +16107,9 @@
       <c r="A730" t="s">
         <v>732</v>
       </c>
+      <c r="B730" t="s">
+        <v>728</v>
+      </c>
       <c r="C730" t="s">
         <v>2641</v>
       </c>
@@ -15830,6 +16118,9 @@
       <c r="A731" t="s">
         <v>733</v>
       </c>
+      <c r="B731" t="s">
+        <v>728</v>
+      </c>
       <c r="C731" t="s">
         <v>2641</v>
       </c>
@@ -15838,6 +16129,9 @@
       <c r="A732" t="s">
         <v>734</v>
       </c>
+      <c r="B732" t="s">
+        <v>728</v>
+      </c>
       <c r="C732" t="s">
         <v>2641</v>
       </c>
@@ -15846,6 +16140,9 @@
       <c r="A733" t="s">
         <v>735</v>
       </c>
+      <c r="B733" t="s">
+        <v>728</v>
+      </c>
       <c r="C733" t="s">
         <v>2641</v>
       </c>
@@ -16021,6 +16318,9 @@
       <c r="A750" t="s">
         <v>752</v>
       </c>
+      <c r="B750" t="s">
+        <v>1599</v>
+      </c>
       <c r="C750" t="s">
         <v>2641</v>
       </c>
@@ -16053,6 +16353,9 @@
       <c r="A754" t="s">
         <v>756</v>
       </c>
+      <c r="B754" t="s">
+        <v>758</v>
+      </c>
       <c r="C754" t="s">
         <v>2641</v>
       </c>
@@ -16061,6 +16364,9 @@
       <c r="A755" t="s">
         <v>757</v>
       </c>
+      <c r="B755" t="s">
+        <v>758</v>
+      </c>
       <c r="C755" t="s">
         <v>2641</v>
       </c>
@@ -16080,6 +16386,9 @@
       <c r="A757" t="s">
         <v>759</v>
       </c>
+      <c r="B757" t="s">
+        <v>758</v>
+      </c>
       <c r="C757" t="s">
         <v>2641</v>
       </c>
@@ -16088,6 +16397,9 @@
       <c r="A758" t="s">
         <v>760</v>
       </c>
+      <c r="B758" t="s">
+        <v>758</v>
+      </c>
       <c r="C758" t="s">
         <v>2641</v>
       </c>
@@ -16096,6 +16408,9 @@
       <c r="A759" t="s">
         <v>761</v>
       </c>
+      <c r="B759" t="s">
+        <v>758</v>
+      </c>
       <c r="C759" t="s">
         <v>2641</v>
       </c>
@@ -16115,6 +16430,9 @@
       <c r="A761" t="s">
         <v>763</v>
       </c>
+      <c r="B761" t="s">
+        <v>758</v>
+      </c>
       <c r="C761" t="s">
         <v>2641</v>
       </c>
@@ -16978,6 +17296,9 @@
       <c r="A840" t="s">
         <v>842</v>
       </c>
+      <c r="B840" t="s">
+        <v>1609</v>
+      </c>
       <c r="C840" t="s">
         <v>2641</v>
       </c>
@@ -17002,6 +17323,9 @@
       <c r="A843" t="s">
         <v>845</v>
       </c>
+      <c r="B843" t="s">
+        <v>1610</v>
+      </c>
       <c r="C843" t="s">
         <v>2641</v>
       </c>
@@ -17244,6 +17568,9 @@
       <c r="A868" t="s">
         <v>870</v>
       </c>
+      <c r="B868" t="s">
+        <v>1620</v>
+      </c>
       <c r="C868" t="s">
         <v>2641</v>
       </c>
@@ -17315,6 +17642,9 @@
       <c r="A875" t="s">
         <v>877</v>
       </c>
+      <c r="B875" t="s">
+        <v>1622</v>
+      </c>
       <c r="C875" t="s">
         <v>2641</v>
       </c>
@@ -17529,6 +17859,9 @@
       <c r="A895" t="s">
         <v>897</v>
       </c>
+      <c r="B895" t="s">
+        <v>893</v>
+      </c>
       <c r="C895" t="s">
         <v>2641</v>
       </c>
@@ -17537,6 +17870,9 @@
       <c r="A896" t="s">
         <v>898</v>
       </c>
+      <c r="B896" t="s">
+        <v>893</v>
+      </c>
       <c r="C896" t="s">
         <v>2641</v>
       </c>
@@ -17655,6 +17991,9 @@
       <c r="A907" t="s">
         <v>909</v>
       </c>
+      <c r="B907" t="s">
+        <v>909</v>
+      </c>
       <c r="C907" t="s">
         <v>2641</v>
       </c>
@@ -17663,6 +18002,9 @@
       <c r="A908" t="s">
         <v>910</v>
       </c>
+      <c r="B908" t="s">
+        <v>909</v>
+      </c>
       <c r="C908" t="s">
         <v>2641</v>
       </c>
@@ -17671,6 +18013,9 @@
       <c r="A909" t="s">
         <v>911</v>
       </c>
+      <c r="B909" t="s">
+        <v>909</v>
+      </c>
       <c r="C909" t="s">
         <v>2641</v>
       </c>
@@ -17794,6 +18139,9 @@
       <c r="A921" t="s">
         <v>923</v>
       </c>
+      <c r="B921" t="s">
+        <v>1628</v>
+      </c>
       <c r="C921" t="s">
         <v>2641</v>
       </c>
@@ -18117,6 +18465,9 @@
       <c r="A952" t="s">
         <v>954</v>
       </c>
+      <c r="B952" t="s">
+        <v>909</v>
+      </c>
       <c r="C952" t="s">
         <v>2641</v>
       </c>
@@ -18125,6 +18476,9 @@
       <c r="A953" t="s">
         <v>955</v>
       </c>
+      <c r="B953" t="s">
+        <v>909</v>
+      </c>
       <c r="C953" t="s">
         <v>2641</v>
       </c>
@@ -18144,6 +18498,9 @@
       <c r="A955" t="s">
         <v>957</v>
       </c>
+      <c r="B955" t="s">
+        <v>1635</v>
+      </c>
       <c r="C955" t="s">
         <v>2641</v>
       </c>
@@ -18292,6 +18649,9 @@
       <c r="A969" t="s">
         <v>971</v>
       </c>
+      <c r="B969" t="s">
+        <v>1638</v>
+      </c>
       <c r="C969" t="s">
         <v>2641</v>
       </c>
@@ -18311,6 +18671,9 @@
       <c r="A971" t="s">
         <v>973</v>
       </c>
+      <c r="B971" t="s">
+        <v>1639</v>
+      </c>
       <c r="C971" t="s">
         <v>2641</v>
       </c>
@@ -18560,6 +18923,9 @@
       <c r="A995" t="s">
         <v>997</v>
       </c>
+      <c r="B995" t="s">
+        <v>1643</v>
+      </c>
       <c r="C995" t="s">
         <v>2641</v>
       </c>
@@ -18652,6 +19018,9 @@
       <c r="A1005" t="s">
         <v>1007</v>
       </c>
+      <c r="B1005" t="s">
+        <v>1648</v>
+      </c>
       <c r="C1005" t="s">
         <v>2641</v>
       </c>
@@ -18668,6 +19037,9 @@
       <c r="A1007" t="s">
         <v>1009</v>
       </c>
+      <c r="B1007" t="s">
+        <v>1009</v>
+      </c>
       <c r="C1007" t="s">
         <v>2641</v>
       </c>
@@ -18698,6 +19070,9 @@
       <c r="A1010" t="s">
         <v>1012</v>
       </c>
+      <c r="B1010" t="s">
+        <v>1652</v>
+      </c>
       <c r="C1010" t="s">
         <v>2641</v>
       </c>
@@ -18780,6 +19155,9 @@
       <c r="A1018" t="s">
         <v>1020</v>
       </c>
+      <c r="B1018" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1018" t="s">
         <v>2641</v>
       </c>
@@ -18788,6 +19166,9 @@
       <c r="A1019" t="s">
         <v>1021</v>
       </c>
+      <c r="B1019" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1019" t="s">
         <v>2641</v>
       </c>
@@ -18796,6 +19177,9 @@
       <c r="A1020" t="s">
         <v>1022</v>
       </c>
+      <c r="B1020" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1020" t="s">
         <v>2641</v>
       </c>
@@ -18804,6 +19188,9 @@
       <c r="A1021" t="s">
         <v>1023</v>
       </c>
+      <c r="B1021" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1021" t="s">
         <v>2641</v>
       </c>
@@ -18812,6 +19199,9 @@
       <c r="A1022" t="s">
         <v>1024</v>
       </c>
+      <c r="B1022" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1022" t="s">
         <v>2641</v>
       </c>
@@ -18820,6 +19210,9 @@
       <c r="A1023" t="s">
         <v>1025</v>
       </c>
+      <c r="B1023" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1023" t="s">
         <v>2641</v>
       </c>
@@ -18828,6 +19221,9 @@
       <c r="A1024" t="s">
         <v>1026</v>
       </c>
+      <c r="B1024" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1024" t="s">
         <v>2641</v>
       </c>
@@ -18836,6 +19232,9 @@
       <c r="A1025" t="s">
         <v>1027</v>
       </c>
+      <c r="B1025" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1025" t="s">
         <v>2641</v>
       </c>
@@ -18844,6 +19243,9 @@
       <c r="A1026" t="s">
         <v>1028</v>
       </c>
+      <c r="B1026" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1026" t="s">
         <v>2641</v>
       </c>
@@ -18852,6 +19254,9 @@
       <c r="A1027" t="s">
         <v>1029</v>
       </c>
+      <c r="B1027" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1027" t="s">
         <v>2641</v>
       </c>
@@ -18860,6 +19265,9 @@
       <c r="A1028" t="s">
         <v>1030</v>
       </c>
+      <c r="B1028" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1028" t="s">
         <v>2641</v>
       </c>
@@ -18868,6 +19276,9 @@
       <c r="A1029" t="s">
         <v>1031</v>
       </c>
+      <c r="B1029" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1029" t="s">
         <v>2641</v>
       </c>
@@ -18876,6 +19287,9 @@
       <c r="A1030" t="s">
         <v>1032</v>
       </c>
+      <c r="B1030" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1030" t="s">
         <v>2641</v>
       </c>
@@ -18947,6 +19361,9 @@
       <c r="A1037" t="s">
         <v>1039</v>
       </c>
+      <c r="B1037" t="s">
+        <v>1667</v>
+      </c>
       <c r="C1037" t="s">
         <v>2641</v>
       </c>
@@ -19010,6 +19427,9 @@
       <c r="A1043" t="s">
         <v>1045</v>
       </c>
+      <c r="B1043" t="s">
+        <v>1669</v>
+      </c>
       <c r="C1043" t="s">
         <v>2641</v>
       </c>
@@ -19029,6 +19449,9 @@
       <c r="A1045" t="s">
         <v>1047</v>
       </c>
+      <c r="B1045" t="s">
+        <v>1795</v>
+      </c>
       <c r="C1045" t="s">
         <v>2641</v>
       </c>
@@ -19102,6 +19525,9 @@
       <c r="A1053" t="s">
         <v>1055</v>
       </c>
+      <c r="B1053" t="s">
+        <v>1676</v>
+      </c>
       <c r="C1053" t="s">
         <v>2641</v>
       </c>
@@ -19129,6 +19555,9 @@
       <c r="A1056" t="s">
         <v>1058</v>
       </c>
+      <c r="B1056" t="s">
+        <v>1678</v>
+      </c>
       <c r="C1056" t="s">
         <v>2641</v>
       </c>
@@ -19148,6 +19577,9 @@
       <c r="A1058" t="s">
         <v>1060</v>
       </c>
+      <c r="B1058" t="s">
+        <v>1059</v>
+      </c>
       <c r="C1058" t="s">
         <v>2641</v>
       </c>
@@ -19337,6 +19769,9 @@
       <c r="A1076" t="s">
         <v>1078</v>
       </c>
+      <c r="B1076" t="s">
+        <v>1073</v>
+      </c>
       <c r="C1076" t="s">
         <v>2641</v>
       </c>
@@ -19372,6 +19807,9 @@
       <c r="A1080" t="s">
         <v>1082</v>
       </c>
+      <c r="B1080" t="s">
+        <v>2463</v>
+      </c>
       <c r="C1080" t="s">
         <v>2641</v>
       </c>
@@ -19380,6 +19818,9 @@
       <c r="A1081" t="s">
         <v>1083</v>
       </c>
+      <c r="B1081" t="s">
+        <v>1684</v>
+      </c>
       <c r="C1081" t="s">
         <v>2641</v>
       </c>
@@ -19533,6 +19974,9 @@
       <c r="A1096" t="s">
         <v>1098</v>
       </c>
+      <c r="B1096" t="s">
+        <v>1097</v>
+      </c>
       <c r="C1096" t="s">
         <v>2641</v>
       </c>
@@ -19780,6 +20224,9 @@
       <c r="A1119" t="s">
         <v>1121</v>
       </c>
+      <c r="B1119" t="s">
+        <v>1121</v>
+      </c>
       <c r="C1119" t="s">
         <v>2641</v>
       </c>
@@ -19834,6 +20281,9 @@
       <c r="A1125" t="s">
         <v>1127</v>
       </c>
+      <c r="B1125" t="s">
+        <v>1126</v>
+      </c>
       <c r="C1125" t="s">
         <v>2641</v>
       </c>
@@ -19842,6 +20292,9 @@
       <c r="A1126" t="s">
         <v>1128</v>
       </c>
+      <c r="B1126" t="s">
+        <v>1126</v>
+      </c>
       <c r="C1126" t="s">
         <v>2641</v>
       </c>
@@ -21598,6 +22051,9 @@
       <c r="A1287" t="s">
         <v>1289</v>
       </c>
+      <c r="B1287" t="s">
+        <v>1705</v>
+      </c>
       <c r="C1287" t="s">
         <v>2641</v>
       </c>
@@ -21628,6 +22084,9 @@
       <c r="A1290" t="s">
         <v>1292</v>
       </c>
+      <c r="B1290" t="s">
+        <v>1290</v>
+      </c>
       <c r="C1290" t="s">
         <v>2641</v>
       </c>
@@ -21729,6 +22188,9 @@
       <c r="A1300" t="s">
         <v>1302</v>
       </c>
+      <c r="B1300" t="s">
+        <v>1707</v>
+      </c>
       <c r="C1300" t="s">
         <v>2641</v>
       </c>
@@ -21889,6 +22351,9 @@
       <c r="A1317" t="s">
         <v>1319</v>
       </c>
+      <c r="B1317" t="s">
+        <v>1319</v>
+      </c>
       <c r="C1317" t="s">
         <v>2641</v>
       </c>
@@ -21897,6 +22362,9 @@
       <c r="A1318" t="s">
         <v>1320</v>
       </c>
+      <c r="B1318" t="s">
+        <v>1319</v>
+      </c>
       <c r="C1318" t="s">
         <v>2641</v>
       </c>
@@ -21905,6 +22373,9 @@
       <c r="A1319" t="s">
         <v>1321</v>
       </c>
+      <c r="B1319" t="s">
+        <v>1321</v>
+      </c>
       <c r="C1319" t="s">
         <v>2641</v>
       </c>
@@ -21913,6 +22384,9 @@
       <c r="A1320" t="s">
         <v>1322</v>
       </c>
+      <c r="B1320" t="s">
+        <v>2649</v>
+      </c>
       <c r="C1320" t="s">
         <v>2641</v>
       </c>
@@ -22032,6 +22506,9 @@
       <c r="A1333" t="s">
         <v>1335</v>
       </c>
+      <c r="B1333" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1333" t="s">
         <v>2641</v>
       </c>
@@ -22040,6 +22517,9 @@
       <c r="A1334" t="s">
         <v>1336</v>
       </c>
+      <c r="B1334" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1334" t="s">
         <v>2641</v>
       </c>
@@ -22059,6 +22539,9 @@
       <c r="A1336" t="s">
         <v>1338</v>
       </c>
+      <c r="B1336" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1336" t="s">
         <v>2641</v>
       </c>
@@ -22067,6 +22550,9 @@
       <c r="A1337" t="s">
         <v>1339</v>
       </c>
+      <c r="B1337" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1337" t="s">
         <v>2641</v>
       </c>
@@ -22105,6 +22591,9 @@
       <c r="A1341" t="s">
         <v>1343</v>
       </c>
+      <c r="B1341" t="s">
+        <v>2650</v>
+      </c>
       <c r="C1341" t="s">
         <v>2641</v>
       </c>
@@ -22124,6 +22613,9 @@
       <c r="A1343" t="s">
         <v>1345</v>
       </c>
+      <c r="B1343" t="s">
+        <v>1344</v>
+      </c>
       <c r="C1343" t="s">
         <v>2641</v>
       </c>
@@ -22132,6 +22624,9 @@
       <c r="A1344" t="s">
         <v>1346</v>
       </c>
+      <c r="B1344" t="s">
+        <v>1344</v>
+      </c>
       <c r="C1344" t="s">
         <v>2641</v>
       </c>
@@ -22167,6 +22662,9 @@
       <c r="A1348" t="s">
         <v>1350</v>
       </c>
+      <c r="B1348" t="s">
+        <v>78</v>
+      </c>
       <c r="C1348">
         <v>3.6</v>
       </c>
@@ -22175,6 +22673,9 @@
       <c r="A1349" t="s">
         <v>1351</v>
       </c>
+      <c r="B1349" t="s">
+        <v>85</v>
+      </c>
       <c r="C1349">
         <v>3.6</v>
       </c>
@@ -22191,6 +22692,9 @@
       <c r="A1351" t="s">
         <v>1353</v>
       </c>
+      <c r="B1351" t="s">
+        <v>97</v>
+      </c>
       <c r="C1351">
         <v>3.6</v>
       </c>
@@ -22199,6 +22703,9 @@
       <c r="A1352" t="s">
         <v>1354</v>
       </c>
+      <c r="B1352" t="s">
+        <v>128</v>
+      </c>
       <c r="C1352">
         <v>3.6</v>
       </c>
@@ -22207,6 +22714,9 @@
       <c r="A1353" t="s">
         <v>1355</v>
       </c>
+      <c r="B1353" t="s">
+        <v>1468</v>
+      </c>
       <c r="C1353">
         <v>3.6</v>
       </c>
@@ -22215,6 +22725,9 @@
       <c r="A1354" t="s">
         <v>1356</v>
       </c>
+      <c r="B1354" t="s">
+        <v>139</v>
+      </c>
       <c r="C1354">
         <v>3.6</v>
       </c>
@@ -22231,6 +22744,9 @@
       <c r="A1356" t="s">
         <v>1358</v>
       </c>
+      <c r="B1356" t="s">
+        <v>166</v>
+      </c>
       <c r="C1356">
         <v>3.6</v>
       </c>
@@ -22279,6 +22795,9 @@
       <c r="A1362" t="s">
         <v>1364</v>
       </c>
+      <c r="B1362" t="s">
+        <v>1518</v>
+      </c>
       <c r="C1362">
         <v>3.6</v>
       </c>
@@ -22287,6 +22806,9 @@
       <c r="A1363" t="s">
         <v>1365</v>
       </c>
+      <c r="B1363" t="s">
+        <v>477</v>
+      </c>
       <c r="C1363">
         <v>3.6</v>
       </c>
@@ -22295,6 +22817,9 @@
       <c r="A1364" t="s">
         <v>1366</v>
       </c>
+      <c r="B1364" t="s">
+        <v>1526</v>
+      </c>
       <c r="C1364">
         <v>3.6</v>
       </c>
@@ -22303,6 +22828,9 @@
       <c r="A1365" t="s">
         <v>1367</v>
       </c>
+      <c r="B1365" t="s">
+        <v>1531</v>
+      </c>
       <c r="C1365">
         <v>3.6</v>
       </c>
@@ -22311,6 +22839,9 @@
       <c r="A1366" t="s">
         <v>1368</v>
       </c>
+      <c r="B1366" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1366">
         <v>3.6</v>
       </c>
@@ -22327,6 +22858,9 @@
       <c r="A1368" t="s">
         <v>1370</v>
       </c>
+      <c r="B1368" t="s">
+        <v>546</v>
+      </c>
       <c r="C1368">
         <v>3.6</v>
       </c>
@@ -22343,6 +22877,9 @@
       <c r="A1370" t="s">
         <v>1372</v>
       </c>
+      <c r="B1370" t="s">
+        <v>1563</v>
+      </c>
       <c r="C1370">
         <v>3.6</v>
       </c>
@@ -22367,6 +22904,9 @@
       <c r="A1373" t="s">
         <v>1375</v>
       </c>
+      <c r="B1373" t="s">
+        <v>1570</v>
+      </c>
       <c r="C1373">
         <v>3.6</v>
       </c>
@@ -22375,6 +22915,9 @@
       <c r="A1374" t="s">
         <v>1376</v>
       </c>
+      <c r="B1374" t="s">
+        <v>1572</v>
+      </c>
       <c r="C1374">
         <v>3.6</v>
       </c>
@@ -22383,6 +22926,9 @@
       <c r="A1375" t="s">
         <v>1377</v>
       </c>
+      <c r="B1375" t="s">
+        <v>626</v>
+      </c>
       <c r="C1375">
         <v>3.6</v>
       </c>
@@ -22391,6 +22937,9 @@
       <c r="A1376" t="s">
         <v>1378</v>
       </c>
+      <c r="B1376" t="s">
+        <v>640</v>
+      </c>
       <c r="C1376">
         <v>3.6</v>
       </c>
@@ -22407,6 +22956,9 @@
       <c r="A1378" t="s">
         <v>1380</v>
       </c>
+      <c r="B1378" t="s">
+        <v>2457</v>
+      </c>
       <c r="C1378">
         <v>3.6</v>
       </c>
@@ -22415,6 +22967,9 @@
       <c r="A1379" t="s">
         <v>1381</v>
       </c>
+      <c r="B1379" t="s">
+        <v>646</v>
+      </c>
       <c r="C1379">
         <v>3.6</v>
       </c>
@@ -22423,6 +22978,9 @@
       <c r="A1380" t="s">
         <v>1382</v>
       </c>
+      <c r="B1380" t="s">
+        <v>656</v>
+      </c>
       <c r="C1380">
         <v>3.6</v>
       </c>
@@ -22431,6 +22989,9 @@
       <c r="A1381" t="s">
         <v>1383</v>
       </c>
+      <c r="B1381" t="s">
+        <v>669</v>
+      </c>
       <c r="C1381">
         <v>3.6</v>
       </c>
@@ -22439,6 +23000,9 @@
       <c r="A1382" t="s">
         <v>1384</v>
       </c>
+      <c r="B1382" t="s">
+        <v>728</v>
+      </c>
       <c r="C1382">
         <v>3.6</v>
       </c>
@@ -22447,6 +23011,9 @@
       <c r="A1383" t="s">
         <v>1385</v>
       </c>
+      <c r="B1383" t="s">
+        <v>1599</v>
+      </c>
       <c r="C1383">
         <v>3.6</v>
       </c>
@@ -22455,6 +23022,9 @@
       <c r="A1384" t="s">
         <v>1386</v>
       </c>
+      <c r="B1384" t="s">
+        <v>1607</v>
+      </c>
       <c r="C1384">
         <v>3.6</v>
       </c>
@@ -22493,6 +23063,9 @@
       <c r="A1388" t="s">
         <v>1390</v>
       </c>
+      <c r="B1388" t="s">
+        <v>893</v>
+      </c>
       <c r="C1388">
         <v>3.6</v>
       </c>
@@ -22509,6 +23082,9 @@
       <c r="A1390" t="s">
         <v>1392</v>
       </c>
+      <c r="B1390" t="s">
+        <v>917</v>
+      </c>
       <c r="C1390">
         <v>3.6</v>
       </c>
@@ -22517,6 +23093,9 @@
       <c r="A1391" t="s">
         <v>1393</v>
       </c>
+      <c r="B1391" t="s">
+        <v>1628</v>
+      </c>
       <c r="C1391">
         <v>3.6</v>
       </c>
@@ -22541,6 +23120,9 @@
       <c r="A1394" t="s">
         <v>1396</v>
       </c>
+      <c r="B1394" t="s">
+        <v>1643</v>
+      </c>
       <c r="C1394">
         <v>3.6</v>
       </c>
@@ -22565,6 +23147,9 @@
       <c r="A1397" t="s">
         <v>1399</v>
       </c>
+      <c r="B1397" t="s">
+        <v>1648</v>
+      </c>
       <c r="C1397">
         <v>3.6</v>
       </c>
@@ -22573,6 +23158,9 @@
       <c r="A1398" t="s">
         <v>1400</v>
       </c>
+      <c r="B1398" t="s">
+        <v>1009</v>
+      </c>
       <c r="C1398">
         <v>3.6</v>
       </c>
@@ -22581,6 +23169,9 @@
       <c r="A1399" t="s">
         <v>1401</v>
       </c>
+      <c r="B1399" t="s">
+        <v>1010</v>
+      </c>
       <c r="C1399">
         <v>3.6</v>
       </c>
@@ -22589,6 +23180,9 @@
       <c r="A1400" t="s">
         <v>1402</v>
       </c>
+      <c r="B1400" t="s">
+        <v>1014</v>
+      </c>
       <c r="C1400">
         <v>3.6</v>
       </c>
@@ -22605,6 +23199,9 @@
       <c r="A1402" t="s">
         <v>1404</v>
       </c>
+      <c r="B1402" t="s">
+        <v>1059</v>
+      </c>
       <c r="C1402">
         <v>3.6</v>
       </c>
@@ -22621,6 +23218,9 @@
       <c r="A1404" t="s">
         <v>1406</v>
       </c>
+      <c r="B1404" t="s">
+        <v>1684</v>
+      </c>
       <c r="C1404">
         <v>3.6</v>
       </c>
@@ -22629,6 +23229,9 @@
       <c r="A1405" t="s">
         <v>1407</v>
       </c>
+      <c r="B1405" t="s">
+        <v>1097</v>
+      </c>
       <c r="C1405">
         <v>3.6</v>
       </c>
@@ -22645,6 +23248,9 @@
       <c r="A1407" t="s">
         <v>1409</v>
       </c>
+      <c r="B1407" t="s">
+        <v>1108</v>
+      </c>
       <c r="C1407">
         <v>3.6</v>
       </c>
@@ -22653,6 +23259,9 @@
       <c r="A1408" t="s">
         <v>1410</v>
       </c>
+      <c r="B1408" t="s">
+        <v>1121</v>
+      </c>
       <c r="C1408">
         <v>3.6</v>
       </c>
@@ -22691,6 +23300,9 @@
       <c r="A1412" t="s">
         <v>1414</v>
       </c>
+      <c r="B1412" t="s">
+        <v>1288</v>
+      </c>
       <c r="C1412">
         <v>3.6</v>
       </c>
@@ -22699,6 +23311,9 @@
       <c r="A1413" t="s">
         <v>1415</v>
       </c>
+      <c r="B1413" t="s">
+        <v>1298</v>
+      </c>
       <c r="C1413">
         <v>3.6</v>
       </c>
@@ -22715,6 +23330,9 @@
       <c r="A1415" t="s">
         <v>1417</v>
       </c>
+      <c r="B1415" t="s">
+        <v>1712</v>
+      </c>
       <c r="C1415">
         <v>3.6</v>
       </c>
@@ -23063,6 +23681,9 @@
       <c r="A1451" t="s">
         <v>1453</v>
       </c>
+      <c r="B1451" t="s">
+        <v>59</v>
+      </c>
       <c r="C1451">
         <v>3.9</v>
       </c>
@@ -23142,6 +23763,9 @@
       <c r="A1459" t="s">
         <v>1461</v>
       </c>
+      <c r="B1459" t="s">
+        <v>2317</v>
+      </c>
       <c r="C1459">
         <v>3.9</v>
       </c>
@@ -23161,6 +23785,9 @@
       <c r="A1461" t="s">
         <v>1463</v>
       </c>
+      <c r="B1461" t="s">
+        <v>1463</v>
+      </c>
       <c r="C1461">
         <v>3.9</v>
       </c>
@@ -23237,6 +23864,9 @@
       <c r="A1469" t="s">
         <v>1471</v>
       </c>
+      <c r="B1469" t="s">
+        <v>166</v>
+      </c>
       <c r="C1469">
         <v>3.9</v>
       </c>
@@ -23245,6 +23875,9 @@
       <c r="A1470" t="s">
         <v>1472</v>
       </c>
+      <c r="B1470" t="s">
+        <v>203</v>
+      </c>
       <c r="C1470">
         <v>3.9</v>
       </c>
@@ -23283,6 +23916,9 @@
       <c r="A1474" t="s">
         <v>1476</v>
       </c>
+      <c r="B1474" t="s">
+        <v>1476</v>
+      </c>
       <c r="C1474">
         <v>3.9</v>
       </c>
@@ -23340,6 +23976,9 @@
       <c r="A1480" t="s">
         <v>1482</v>
       </c>
+      <c r="B1480" t="s">
+        <v>235</v>
+      </c>
       <c r="C1480">
         <v>3.9</v>
       </c>
@@ -23348,6 +23987,9 @@
       <c r="A1481" t="s">
         <v>1483</v>
       </c>
+      <c r="B1481" t="s">
+        <v>1483</v>
+      </c>
       <c r="C1481">
         <v>3.9</v>
       </c>
@@ -23356,6 +23998,9 @@
       <c r="A1482" t="s">
         <v>1484</v>
       </c>
+      <c r="B1482" t="s">
+        <v>1484</v>
+      </c>
       <c r="C1482">
         <v>3.9</v>
       </c>
@@ -23375,6 +24020,9 @@
       <c r="A1484" t="s">
         <v>1486</v>
       </c>
+      <c r="B1484" t="s">
+        <v>1486</v>
+      </c>
       <c r="C1484">
         <v>3.9</v>
       </c>
@@ -23383,6 +24031,9 @@
       <c r="A1485" t="s">
         <v>1487</v>
       </c>
+      <c r="B1485" t="s">
+        <v>1487</v>
+      </c>
       <c r="C1485">
         <v>3.9</v>
       </c>
@@ -23391,6 +24042,9 @@
       <c r="A1486" t="s">
         <v>1488</v>
       </c>
+      <c r="B1486" t="s">
+        <v>1748</v>
+      </c>
       <c r="C1486">
         <v>3.9</v>
       </c>
@@ -23410,6 +24064,9 @@
       <c r="A1488" t="s">
         <v>1490</v>
       </c>
+      <c r="B1488" t="s">
+        <v>258</v>
+      </c>
       <c r="C1488">
         <v>3.9</v>
       </c>
@@ -23418,6 +24075,9 @@
       <c r="A1489" t="s">
         <v>1491</v>
       </c>
+      <c r="B1489" t="s">
+        <v>1491</v>
+      </c>
       <c r="C1489">
         <v>3.9</v>
       </c>
@@ -23459,6 +24119,9 @@
       <c r="A1493" t="s">
         <v>1495</v>
       </c>
+      <c r="B1493" t="s">
+        <v>266</v>
+      </c>
       <c r="C1493">
         <v>3.9</v>
       </c>
@@ -23467,6 +24130,9 @@
       <c r="A1494" t="s">
         <v>1496</v>
       </c>
+      <c r="B1494" t="s">
+        <v>266</v>
+      </c>
       <c r="C1494">
         <v>3.9</v>
       </c>
@@ -23475,6 +24141,9 @@
       <c r="A1495" t="s">
         <v>1497</v>
       </c>
+      <c r="B1495" t="s">
+        <v>266</v>
+      </c>
       <c r="C1495">
         <v>3.9</v>
       </c>
@@ -23483,6 +24152,9 @@
       <c r="A1496" t="s">
         <v>1498</v>
       </c>
+      <c r="B1496" t="s">
+        <v>266</v>
+      </c>
       <c r="C1496">
         <v>3.9</v>
       </c>
@@ -23491,6 +24163,9 @@
       <c r="A1497" t="s">
         <v>1499</v>
       </c>
+      <c r="B1497" t="s">
+        <v>266</v>
+      </c>
       <c r="C1497">
         <v>3.9</v>
       </c>
@@ -23499,6 +24174,9 @@
       <c r="A1498" t="s">
         <v>1500</v>
       </c>
+      <c r="B1498" t="s">
+        <v>266</v>
+      </c>
       <c r="C1498">
         <v>3.9</v>
       </c>
@@ -23507,6 +24185,9 @@
       <c r="A1499" t="s">
         <v>1501</v>
       </c>
+      <c r="B1499" t="s">
+        <v>266</v>
+      </c>
       <c r="C1499">
         <v>3.9</v>
       </c>
@@ -23515,6 +24196,9 @@
       <c r="A1500" t="s">
         <v>1502</v>
       </c>
+      <c r="B1500" t="s">
+        <v>266</v>
+      </c>
       <c r="C1500">
         <v>3.9</v>
       </c>
@@ -23523,6 +24207,9 @@
       <c r="A1501" t="s">
         <v>1503</v>
       </c>
+      <c r="B1501" t="s">
+        <v>266</v>
+      </c>
       <c r="C1501">
         <v>3.9</v>
       </c>
@@ -23531,6 +24218,9 @@
       <c r="A1502" t="s">
         <v>1504</v>
       </c>
+      <c r="B1502" t="s">
+        <v>266</v>
+      </c>
       <c r="C1502">
         <v>3.9</v>
       </c>
@@ -23539,6 +24229,9 @@
       <c r="A1503" t="s">
         <v>1505</v>
       </c>
+      <c r="B1503" t="s">
+        <v>266</v>
+      </c>
       <c r="C1503">
         <v>3.9</v>
       </c>
@@ -23547,6 +24240,9 @@
       <c r="A1504" t="s">
         <v>1506</v>
       </c>
+      <c r="B1504" t="s">
+        <v>266</v>
+      </c>
       <c r="C1504">
         <v>3.9</v>
       </c>
@@ -23555,6 +24251,9 @@
       <c r="A1505" t="s">
         <v>1507</v>
       </c>
+      <c r="B1505" t="s">
+        <v>266</v>
+      </c>
       <c r="C1505">
         <v>3.9</v>
       </c>
@@ -23563,6 +24262,9 @@
       <c r="A1506" t="s">
         <v>1508</v>
       </c>
+      <c r="B1506" t="s">
+        <v>266</v>
+      </c>
       <c r="C1506">
         <v>3.9</v>
       </c>
@@ -23593,6 +24295,9 @@
       <c r="A1509" t="s">
         <v>1511</v>
       </c>
+      <c r="B1509" t="s">
+        <v>1511</v>
+      </c>
       <c r="C1509">
         <v>3.9</v>
       </c>
@@ -23612,6 +24317,9 @@
       <c r="A1511" t="s">
         <v>1513</v>
       </c>
+      <c r="B1511" t="s">
+        <v>1513</v>
+      </c>
       <c r="C1511">
         <v>3.9</v>
       </c>
@@ -23655,6 +24363,9 @@
       <c r="A1516" t="s">
         <v>1518</v>
       </c>
+      <c r="B1516" t="s">
+        <v>1518</v>
+      </c>
       <c r="C1516">
         <v>3.9</v>
       </c>
@@ -23663,6 +24374,9 @@
       <c r="A1517" t="s">
         <v>1519</v>
       </c>
+      <c r="B1517" t="s">
+        <v>1518</v>
+      </c>
       <c r="C1517">
         <v>3.9</v>
       </c>
@@ -23671,6 +24385,9 @@
       <c r="A1518" t="s">
         <v>1520</v>
       </c>
+      <c r="B1518" t="s">
+        <v>1520</v>
+      </c>
       <c r="C1518">
         <v>3.9</v>
       </c>
@@ -23712,6 +24429,9 @@
       <c r="A1522" t="s">
         <v>1524</v>
       </c>
+      <c r="B1522" t="s">
+        <v>477</v>
+      </c>
       <c r="C1522">
         <v>3.9</v>
       </c>
@@ -23720,6 +24440,9 @@
       <c r="A1523" t="s">
         <v>1525</v>
       </c>
+      <c r="B1523" t="s">
+        <v>477</v>
+      </c>
       <c r="C1523">
         <v>3.9</v>
       </c>
@@ -23728,6 +24451,9 @@
       <c r="A1524" t="s">
         <v>1526</v>
       </c>
+      <c r="B1524" t="s">
+        <v>1526</v>
+      </c>
       <c r="C1524">
         <v>3.9</v>
       </c>
@@ -23736,6 +24462,9 @@
       <c r="A1525" t="s">
         <v>1527</v>
       </c>
+      <c r="B1525" t="s">
+        <v>1526</v>
+      </c>
       <c r="C1525">
         <v>3.9</v>
       </c>
@@ -23788,6 +24517,9 @@
       <c r="A1530" t="s">
         <v>1532</v>
       </c>
+      <c r="B1530" t="s">
+        <v>1531</v>
+      </c>
       <c r="C1530">
         <v>3.9</v>
       </c>
@@ -23796,6 +24528,9 @@
       <c r="A1531" t="s">
         <v>1533</v>
       </c>
+      <c r="B1531" t="s">
+        <v>1533</v>
+      </c>
       <c r="C1531">
         <v>3.9</v>
       </c>
@@ -23804,6 +24539,9 @@
       <c r="A1532" t="s">
         <v>1534</v>
       </c>
+      <c r="B1532" t="s">
+        <v>1533</v>
+      </c>
       <c r="C1532">
         <v>3.9</v>
       </c>
@@ -23812,6 +24550,9 @@
       <c r="A1533" t="s">
         <v>1535</v>
       </c>
+      <c r="B1533" t="s">
+        <v>2646</v>
+      </c>
       <c r="C1533">
         <v>3.9</v>
       </c>
@@ -23820,6 +24561,9 @@
       <c r="A1534" t="s">
         <v>1536</v>
       </c>
+      <c r="B1534" t="s">
+        <v>2647</v>
+      </c>
       <c r="C1534">
         <v>3.9</v>
       </c>
@@ -23850,6 +24594,9 @@
       <c r="A1537" t="s">
         <v>1539</v>
       </c>
+      <c r="B1537" t="s">
+        <v>522</v>
+      </c>
       <c r="C1537">
         <v>3.9</v>
       </c>
@@ -23858,6 +24605,9 @@
       <c r="A1538" t="s">
         <v>1540</v>
       </c>
+      <c r="B1538" t="s">
+        <v>522</v>
+      </c>
       <c r="C1538">
         <v>3.9</v>
       </c>
@@ -23866,6 +24616,9 @@
       <c r="A1539" t="s">
         <v>1541</v>
       </c>
+      <c r="B1539" t="s">
+        <v>522</v>
+      </c>
       <c r="C1539">
         <v>3.9</v>
       </c>
@@ -23874,6 +24627,9 @@
       <c r="A1540" t="s">
         <v>1542</v>
       </c>
+      <c r="B1540" t="s">
+        <v>522</v>
+      </c>
       <c r="C1540">
         <v>3.9</v>
       </c>
@@ -23882,6 +24638,9 @@
       <c r="A1541" t="s">
         <v>1543</v>
       </c>
+      <c r="B1541" t="s">
+        <v>522</v>
+      </c>
       <c r="C1541">
         <v>3.9</v>
       </c>
@@ -23890,6 +24649,9 @@
       <c r="A1542" t="s">
         <v>1544</v>
       </c>
+      <c r="B1542" t="s">
+        <v>522</v>
+      </c>
       <c r="C1542">
         <v>3.9</v>
       </c>
@@ -23898,6 +24660,9 @@
       <c r="A1543" t="s">
         <v>1545</v>
       </c>
+      <c r="B1543" t="s">
+        <v>522</v>
+      </c>
       <c r="C1543">
         <v>3.9</v>
       </c>
@@ -23906,6 +24671,9 @@
       <c r="A1544" t="s">
         <v>1546</v>
       </c>
+      <c r="B1544" t="s">
+        <v>522</v>
+      </c>
       <c r="C1544">
         <v>3.9</v>
       </c>
@@ -23914,6 +24682,9 @@
       <c r="A1545" t="s">
         <v>1547</v>
       </c>
+      <c r="B1545" t="s">
+        <v>522</v>
+      </c>
       <c r="C1545">
         <v>3.9</v>
       </c>
@@ -23922,6 +24693,9 @@
       <c r="A1546" t="s">
         <v>1548</v>
       </c>
+      <c r="B1546" t="s">
+        <v>522</v>
+      </c>
       <c r="C1546">
         <v>3.9</v>
       </c>
@@ -23930,6 +24704,9 @@
       <c r="A1547" t="s">
         <v>1549</v>
       </c>
+      <c r="B1547" t="s">
+        <v>522</v>
+      </c>
       <c r="C1547">
         <v>3.9</v>
       </c>
@@ -23938,6 +24715,9 @@
       <c r="A1548" t="s">
         <v>1550</v>
       </c>
+      <c r="B1548" t="s">
+        <v>522</v>
+      </c>
       <c r="C1548">
         <v>3.9</v>
       </c>
@@ -23946,6 +24726,9 @@
       <c r="A1549" t="s">
         <v>1551</v>
       </c>
+      <c r="B1549" t="s">
+        <v>522</v>
+      </c>
       <c r="C1549">
         <v>3.9</v>
       </c>
@@ -23954,6 +24737,9 @@
       <c r="A1550" t="s">
         <v>1552</v>
       </c>
+      <c r="B1550" t="s">
+        <v>522</v>
+      </c>
       <c r="C1550">
         <v>3.9</v>
       </c>
@@ -23984,6 +24770,9 @@
       <c r="A1553" t="s">
         <v>1555</v>
       </c>
+      <c r="B1553" t="s">
+        <v>1555</v>
+      </c>
       <c r="C1553">
         <v>3.9</v>
       </c>
@@ -23992,6 +24781,9 @@
       <c r="A1554" t="s">
         <v>1556</v>
       </c>
+      <c r="B1554" t="s">
+        <v>1556</v>
+      </c>
       <c r="C1554">
         <v>3.9</v>
       </c>
@@ -24030,6 +24822,9 @@
       <c r="A1558" t="s">
         <v>1560</v>
       </c>
+      <c r="B1558" t="s">
+        <v>546</v>
+      </c>
       <c r="C1558">
         <v>3.9</v>
       </c>
@@ -24038,6 +24833,9 @@
       <c r="A1559" t="s">
         <v>1561</v>
       </c>
+      <c r="B1559" t="s">
+        <v>546</v>
+      </c>
       <c r="C1559">
         <v>3.9</v>
       </c>
@@ -24054,6 +24852,9 @@
       <c r="A1561" t="s">
         <v>1563</v>
       </c>
+      <c r="B1561" t="s">
+        <v>1563</v>
+      </c>
       <c r="C1561">
         <v>3.9</v>
       </c>
@@ -24062,6 +24863,9 @@
       <c r="A1562" t="s">
         <v>1564</v>
       </c>
+      <c r="B1562" t="s">
+        <v>1563</v>
+      </c>
       <c r="C1562">
         <v>3.9</v>
       </c>
@@ -24100,6 +24904,9 @@
       <c r="A1566" t="s">
         <v>1568</v>
       </c>
+      <c r="B1566" t="s">
+        <v>599</v>
+      </c>
       <c r="C1566">
         <v>3.9</v>
       </c>
@@ -24108,6 +24915,9 @@
       <c r="A1567" t="s">
         <v>1569</v>
       </c>
+      <c r="B1567" t="s">
+        <v>599</v>
+      </c>
       <c r="C1567">
         <v>3.9</v>
       </c>
@@ -24116,6 +24926,9 @@
       <c r="A1568" t="s">
         <v>1570</v>
       </c>
+      <c r="B1568" t="s">
+        <v>1570</v>
+      </c>
       <c r="C1568">
         <v>3.9</v>
       </c>
@@ -24124,6 +24937,9 @@
       <c r="A1569" t="s">
         <v>1571</v>
       </c>
+      <c r="B1569" t="s">
+        <v>1570</v>
+      </c>
       <c r="C1569">
         <v>3.9</v>
       </c>
@@ -24132,6 +24948,9 @@
       <c r="A1570" t="s">
         <v>1572</v>
       </c>
+      <c r="B1570" t="s">
+        <v>1572</v>
+      </c>
       <c r="C1570">
         <v>3.9</v>
       </c>
@@ -24140,6 +24959,9 @@
       <c r="A1571" t="s">
         <v>1573</v>
       </c>
+      <c r="B1571" t="s">
+        <v>1572</v>
+      </c>
       <c r="C1571">
         <v>3.9</v>
       </c>
@@ -24156,6 +24978,9 @@
       <c r="A1573" t="s">
         <v>1575</v>
       </c>
+      <c r="B1573" t="s">
+        <v>626</v>
+      </c>
       <c r="C1573">
         <v>3.9</v>
       </c>
@@ -24183,6 +25008,9 @@
       <c r="A1576" t="s">
         <v>1578</v>
       </c>
+      <c r="B1576" t="s">
+        <v>631</v>
+      </c>
       <c r="C1576">
         <v>3.9</v>
       </c>
@@ -24191,6 +25019,9 @@
       <c r="A1577" t="s">
         <v>1579</v>
       </c>
+      <c r="B1577" t="s">
+        <v>631</v>
+      </c>
       <c r="C1577">
         <v>3.9</v>
       </c>
@@ -24199,6 +25030,9 @@
       <c r="A1578" t="s">
         <v>1580</v>
       </c>
+      <c r="B1578" t="s">
+        <v>631</v>
+      </c>
       <c r="C1578">
         <v>3.9</v>
       </c>
@@ -24218,6 +25052,9 @@
       <c r="A1580" t="s">
         <v>1582</v>
       </c>
+      <c r="B1580" t="s">
+        <v>640</v>
+      </c>
       <c r="C1580">
         <v>3.9</v>
       </c>
@@ -24248,6 +25085,9 @@
       <c r="A1583" t="s">
         <v>1585</v>
       </c>
+      <c r="B1583" t="s">
+        <v>2457</v>
+      </c>
       <c r="C1583">
         <v>3.9</v>
       </c>
@@ -24267,6 +25107,9 @@
       <c r="A1585" t="s">
         <v>1587</v>
       </c>
+      <c r="B1585" t="s">
+        <v>656</v>
+      </c>
       <c r="C1585">
         <v>3.9</v>
       </c>
@@ -24297,6 +25140,9 @@
       <c r="A1588" t="s">
         <v>1590</v>
       </c>
+      <c r="B1588" t="s">
+        <v>728</v>
+      </c>
       <c r="C1588">
         <v>3.9</v>
       </c>
@@ -24305,6 +25151,9 @@
       <c r="A1589" t="s">
         <v>1591</v>
       </c>
+      <c r="B1589" t="s">
+        <v>728</v>
+      </c>
       <c r="C1589">
         <v>3.9</v>
       </c>
@@ -24313,6 +25162,9 @@
       <c r="A1590" t="s">
         <v>1592</v>
       </c>
+      <c r="B1590" t="s">
+        <v>728</v>
+      </c>
       <c r="C1590">
         <v>3.9</v>
       </c>
@@ -24321,6 +25173,9 @@
       <c r="A1591" t="s">
         <v>1593</v>
       </c>
+      <c r="B1591" t="s">
+        <v>728</v>
+      </c>
       <c r="C1591">
         <v>3.9</v>
       </c>
@@ -24329,6 +25184,9 @@
       <c r="A1592" t="s">
         <v>1594</v>
       </c>
+      <c r="B1592" t="s">
+        <v>728</v>
+      </c>
       <c r="C1592">
         <v>3.9</v>
       </c>
@@ -24337,6 +25195,9 @@
       <c r="A1593" t="s">
         <v>1595</v>
       </c>
+      <c r="B1593" t="s">
+        <v>728</v>
+      </c>
       <c r="C1593">
         <v>3.9</v>
       </c>
@@ -24345,6 +25206,9 @@
       <c r="A1594" t="s">
         <v>1596</v>
       </c>
+      <c r="B1594" t="s">
+        <v>728</v>
+      </c>
       <c r="C1594">
         <v>3.9</v>
       </c>
@@ -24369,6 +25233,9 @@
       <c r="A1597" t="s">
         <v>1599</v>
       </c>
+      <c r="B1597" t="s">
+        <v>1599</v>
+      </c>
       <c r="C1597">
         <v>3.9</v>
       </c>
@@ -24377,6 +25244,9 @@
       <c r="A1598" t="s">
         <v>1600</v>
       </c>
+      <c r="B1598" t="s">
+        <v>1599</v>
+      </c>
       <c r="C1598">
         <v>3.9</v>
       </c>
@@ -24385,6 +25255,9 @@
       <c r="A1599" t="s">
         <v>1601</v>
       </c>
+      <c r="B1599" t="s">
+        <v>758</v>
+      </c>
       <c r="C1599">
         <v>3.9</v>
       </c>
@@ -24393,6 +25266,9 @@
       <c r="A1600" t="s">
         <v>1602</v>
       </c>
+      <c r="B1600" t="s">
+        <v>758</v>
+      </c>
       <c r="C1600">
         <v>3.9</v>
       </c>
@@ -24412,6 +25288,9 @@
       <c r="A1602" t="s">
         <v>1604</v>
       </c>
+      <c r="B1602" t="s">
+        <v>758</v>
+      </c>
       <c r="C1602">
         <v>3.9</v>
       </c>
@@ -24420,6 +25299,9 @@
       <c r="A1603" t="s">
         <v>1605</v>
       </c>
+      <c r="B1603" t="s">
+        <v>758</v>
+      </c>
       <c r="C1603">
         <v>3.9</v>
       </c>
@@ -24428,6 +25310,9 @@
       <c r="A1604" t="s">
         <v>1606</v>
       </c>
+      <c r="B1604" t="s">
+        <v>758</v>
+      </c>
       <c r="C1604">
         <v>3.9</v>
       </c>
@@ -24458,6 +25343,9 @@
       <c r="A1607" t="s">
         <v>1609</v>
       </c>
+      <c r="B1607" t="s">
+        <v>1609</v>
+      </c>
       <c r="C1607">
         <v>3.9</v>
       </c>
@@ -24466,6 +25354,9 @@
       <c r="A1608" t="s">
         <v>1610</v>
       </c>
+      <c r="B1608" t="s">
+        <v>1610</v>
+      </c>
       <c r="C1608">
         <v>3.9</v>
       </c>
@@ -24555,6 +25446,9 @@
       <c r="A1618" t="s">
         <v>1620</v>
       </c>
+      <c r="B1618" t="s">
+        <v>1620</v>
+      </c>
       <c r="C1618">
         <v>3.9</v>
       </c>
@@ -24574,6 +25468,9 @@
       <c r="A1620" t="s">
         <v>1622</v>
       </c>
+      <c r="B1620" t="s">
+        <v>1622</v>
+      </c>
       <c r="C1620">
         <v>3.9</v>
       </c>
@@ -24582,6 +25479,9 @@
       <c r="A1621" t="s">
         <v>1623</v>
       </c>
+      <c r="B1621" t="s">
+        <v>893</v>
+      </c>
       <c r="C1621">
         <v>3.9</v>
       </c>
@@ -24590,6 +25490,9 @@
       <c r="A1622" t="s">
         <v>1624</v>
       </c>
+      <c r="B1622" t="s">
+        <v>893</v>
+      </c>
       <c r="C1622">
         <v>3.9</v>
       </c>
@@ -24598,6 +25501,9 @@
       <c r="A1623" t="s">
         <v>1625</v>
       </c>
+      <c r="B1623" t="s">
+        <v>909</v>
+      </c>
       <c r="C1623">
         <v>3.9</v>
       </c>
@@ -24622,6 +25528,9 @@
       <c r="A1626" t="s">
         <v>1628</v>
       </c>
+      <c r="B1626" t="s">
+        <v>1628</v>
+      </c>
       <c r="C1626">
         <v>3.9</v>
       </c>
@@ -24630,6 +25539,9 @@
       <c r="A1627" t="s">
         <v>1629</v>
       </c>
+      <c r="B1627" t="s">
+        <v>1628</v>
+      </c>
       <c r="C1627">
         <v>3.9</v>
       </c>
@@ -24668,6 +25580,9 @@
       <c r="A1631" t="s">
         <v>1633</v>
       </c>
+      <c r="B1631" t="s">
+        <v>909</v>
+      </c>
       <c r="C1631">
         <v>3.9</v>
       </c>
@@ -24676,6 +25591,9 @@
       <c r="A1632" t="s">
         <v>1634</v>
       </c>
+      <c r="B1632" t="s">
+        <v>909</v>
+      </c>
       <c r="C1632">
         <v>3.9</v>
       </c>
@@ -24684,6 +25602,9 @@
       <c r="A1633" t="s">
         <v>1635</v>
       </c>
+      <c r="B1633" t="s">
+        <v>1635</v>
+      </c>
       <c r="C1633">
         <v>3.9</v>
       </c>
@@ -24711,6 +25632,9 @@
       <c r="A1636" t="s">
         <v>1638</v>
       </c>
+      <c r="B1636" t="s">
+        <v>1638</v>
+      </c>
       <c r="C1636">
         <v>3.9</v>
       </c>
@@ -24719,6 +25643,9 @@
       <c r="A1637" t="s">
         <v>1639</v>
       </c>
+      <c r="B1637" t="s">
+        <v>1639</v>
+      </c>
       <c r="C1637">
         <v>3.9</v>
       </c>
@@ -24762,6 +25689,9 @@
       <c r="A1642" t="s">
         <v>1644</v>
       </c>
+      <c r="B1642" t="s">
+        <v>1643</v>
+      </c>
       <c r="C1642">
         <v>3.9</v>
       </c>
@@ -24794,6 +25724,9 @@
       <c r="A1646" t="s">
         <v>1648</v>
       </c>
+      <c r="B1646" t="s">
+        <v>1648</v>
+      </c>
       <c r="C1646">
         <v>3.9</v>
       </c>
@@ -24802,6 +25735,9 @@
       <c r="A1647" t="s">
         <v>1649</v>
       </c>
+      <c r="B1647" t="s">
+        <v>1648</v>
+      </c>
       <c r="C1647">
         <v>3.9</v>
       </c>
@@ -24810,6 +25746,9 @@
       <c r="A1648" t="s">
         <v>1650</v>
       </c>
+      <c r="B1648" t="s">
+        <v>2651</v>
+      </c>
       <c r="C1648">
         <v>3.9</v>
       </c>
@@ -24829,6 +25768,9 @@
       <c r="A1650" t="s">
         <v>1652</v>
       </c>
+      <c r="B1650" t="s">
+        <v>1652</v>
+      </c>
       <c r="C1650">
         <v>3.9</v>
       </c>
@@ -24848,6 +25790,9 @@
       <c r="A1652" t="s">
         <v>1654</v>
       </c>
+      <c r="B1652" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1652">
         <v>3.9</v>
       </c>
@@ -24856,6 +25801,9 @@
       <c r="A1653" t="s">
         <v>1655</v>
       </c>
+      <c r="B1653" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1653">
         <v>3.9</v>
       </c>
@@ -24864,6 +25812,9 @@
       <c r="A1654" t="s">
         <v>1656</v>
       </c>
+      <c r="B1654" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1654">
         <v>3.9</v>
       </c>
@@ -24872,6 +25823,9 @@
       <c r="A1655" t="s">
         <v>1657</v>
       </c>
+      <c r="B1655" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1655">
         <v>3.9</v>
       </c>
@@ -24880,6 +25834,9 @@
       <c r="A1656" t="s">
         <v>1658</v>
       </c>
+      <c r="B1656" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1656">
         <v>3.9</v>
       </c>
@@ -24888,6 +25845,9 @@
       <c r="A1657" t="s">
         <v>1659</v>
       </c>
+      <c r="B1657" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1657">
         <v>3.9</v>
       </c>
@@ -24896,6 +25856,9 @@
       <c r="A1658" t="s">
         <v>1660</v>
       </c>
+      <c r="B1658" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1658">
         <v>3.9</v>
       </c>
@@ -24904,6 +25867,9 @@
       <c r="A1659" t="s">
         <v>1661</v>
       </c>
+      <c r="B1659" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1659">
         <v>3.9</v>
       </c>
@@ -24912,6 +25878,9 @@
       <c r="A1660" t="s">
         <v>1662</v>
       </c>
+      <c r="B1660" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1660">
         <v>3.9</v>
       </c>
@@ -24920,6 +25889,9 @@
       <c r="A1661" t="s">
         <v>1663</v>
       </c>
+      <c r="B1661" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1661">
         <v>3.9</v>
       </c>
@@ -24928,6 +25900,9 @@
       <c r="A1662" t="s">
         <v>1664</v>
       </c>
+      <c r="B1662" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1662">
         <v>3.9</v>
       </c>
@@ -24936,6 +25911,9 @@
       <c r="A1663" t="s">
         <v>1665</v>
       </c>
+      <c r="B1663" t="s">
+        <v>1019</v>
+      </c>
       <c r="C1663">
         <v>3.9</v>
       </c>
@@ -25045,6 +26023,9 @@
       <c r="A1674" t="s">
         <v>1676</v>
       </c>
+      <c r="B1674" t="s">
+        <v>1676</v>
+      </c>
       <c r="C1674">
         <v>3.9</v>
       </c>
@@ -25061,6 +26042,9 @@
       <c r="A1676" t="s">
         <v>1678</v>
       </c>
+      <c r="B1676" t="s">
+        <v>1678</v>
+      </c>
       <c r="C1676">
         <v>3.9</v>
       </c>
@@ -25129,6 +26113,9 @@
       <c r="A1683" t="s">
         <v>1685</v>
       </c>
+      <c r="B1683" t="s">
+        <v>1684</v>
+      </c>
       <c r="C1683">
         <v>3.9</v>
       </c>
@@ -25159,6 +26146,9 @@
       <c r="A1686" t="s">
         <v>1688</v>
       </c>
+      <c r="B1686" t="s">
+        <v>1097</v>
+      </c>
       <c r="C1686">
         <v>3.9</v>
       </c>
@@ -25260,6 +26250,9 @@
       <c r="A1696" t="s">
         <v>1698</v>
       </c>
+      <c r="B1696" t="s">
+        <v>1126</v>
+      </c>
       <c r="C1696">
         <v>3.9</v>
       </c>
@@ -25325,6 +26318,9 @@
       <c r="A1703" t="s">
         <v>1705</v>
       </c>
+      <c r="B1703" t="s">
+        <v>1705</v>
+      </c>
       <c r="C1703">
         <v>3.9</v>
       </c>
@@ -25344,6 +26340,9 @@
       <c r="A1705" t="s">
         <v>1707</v>
       </c>
+      <c r="B1705" t="s">
+        <v>1707</v>
+      </c>
       <c r="C1705">
         <v>3.9</v>
       </c>
@@ -25384,6 +26383,9 @@
       <c r="A1710" t="s">
         <v>1712</v>
       </c>
+      <c r="B1710" t="s">
+        <v>1712</v>
+      </c>
       <c r="C1710">
         <v>3.9</v>
       </c>
@@ -25403,6 +26405,9 @@
       <c r="A1712" t="s">
         <v>1714</v>
       </c>
+      <c r="B1712" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1712">
         <v>3.9</v>
       </c>
@@ -25411,6 +26416,9 @@
       <c r="A1713" t="s">
         <v>1715</v>
       </c>
+      <c r="B1713" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1713">
         <v>3.9</v>
       </c>
@@ -25419,6 +26427,9 @@
       <c r="A1714" t="s">
         <v>1716</v>
       </c>
+      <c r="B1714" t="s">
+        <v>1334</v>
+      </c>
       <c r="C1714">
         <v>3.9</v>
       </c>
@@ -25427,6 +26438,9 @@
       <c r="A1715" t="s">
         <v>1717</v>
       </c>
+      <c r="B1715" t="s">
+        <v>2650</v>
+      </c>
       <c r="C1715">
         <v>3.9</v>
       </c>
@@ -25435,6 +26449,9 @@
       <c r="A1716" t="s">
         <v>1718</v>
       </c>
+      <c r="B1716" t="s">
+        <v>1344</v>
+      </c>
       <c r="C1716">
         <v>3.9</v>
       </c>
@@ -25751,6 +26768,9 @@
     </row>
     <row r="1746" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1746" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1746" t="s">
         <v>1748</v>
       </c>
       <c r="C1746" t="s">
